--- a/research/traditional_assets/database/data/cyprus/cyprus_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08415</v>
+        <v>0.0539</v>
       </c>
       <c r="E2">
-        <v>0.257</v>
+        <v>0.061</v>
       </c>
       <c r="G2">
-        <v>0.12126953125</v>
+        <v>0.3512807881773399</v>
       </c>
       <c r="H2">
-        <v>0.12126953125</v>
+        <v>0.3512807881773399</v>
       </c>
       <c r="I2">
-        <v>0.30203125</v>
+        <v>0.1629064039408867</v>
       </c>
       <c r="J2">
-        <v>0.2337896164399074</v>
+        <v>0.1572466438039708</v>
       </c>
       <c r="K2">
-        <v>14.715</v>
+        <v>6.179</v>
       </c>
       <c r="L2">
-        <v>0.28740234375</v>
+        <v>0.152192118226601</v>
       </c>
       <c r="M2">
-        <v>6.93</v>
+        <v>4.89</v>
       </c>
       <c r="N2">
-        <v>0.08774373259052924</v>
+        <v>0.06799221357063404</v>
       </c>
       <c r="O2">
-        <v>0.4709480122324159</v>
+        <v>0.7913901925877973</v>
       </c>
       <c r="P2">
-        <v>6.93</v>
+        <v>4.89</v>
       </c>
       <c r="Q2">
-        <v>0.08774373259052924</v>
+        <v>0.06799221357063404</v>
       </c>
       <c r="R2">
-        <v>0.4709480122324159</v>
+        <v>0.7913901925877973</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15.52</v>
+        <v>14.75</v>
       </c>
       <c r="V2">
-        <v>0.1965054444163079</v>
+        <v>0.2050889877641824</v>
       </c>
       <c r="W2">
-        <v>0.1892753292319523</v>
+        <v>0.02246750756099497</v>
       </c>
       <c r="X2">
-        <v>0.08638882542583165</v>
+        <v>0.1153636277181256</v>
       </c>
       <c r="Y2">
-        <v>0.1028865038061207</v>
+        <v>-0.09289612015713064</v>
       </c>
       <c r="Z2">
-        <v>1.20196257952438</v>
+        <v>0.8270860495436768</v>
       </c>
       <c r="AA2">
-        <v>0.2118386582861172</v>
+        <v>0.04438685171063248</v>
       </c>
       <c r="AB2">
-        <v>0.0676567357707558</v>
+        <v>0.1062045512964268</v>
       </c>
       <c r="AC2">
-        <v>0.1441819225153614</v>
+        <v>-0.06181769958579437</v>
       </c>
       <c r="AD2">
-        <v>4.893000000000001</v>
+        <v>3.113</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.893000000000001</v>
+        <v>3.113</v>
       </c>
       <c r="AG2">
-        <v>-10.627</v>
+        <v>-11.637</v>
       </c>
       <c r="AH2">
-        <v>0.05833820180511011</v>
+        <v>0.04148841176548985</v>
       </c>
       <c r="AI2">
-        <v>0.07513474502096036</v>
+        <v>0.05127402697939486</v>
       </c>
       <c r="AJ2">
-        <v>-0.1554723274764823</v>
+        <v>-0.1930394970389662</v>
       </c>
       <c r="AK2">
-        <v>-0.2142410741285809</v>
+        <v>-0.253181907186215</v>
       </c>
       <c r="AL2">
-        <v>0.174</v>
+        <v>0.11</v>
       </c>
       <c r="AM2">
-        <v>0.174</v>
+        <v>0.11</v>
       </c>
       <c r="AN2">
-        <v>0.3075230972283327</v>
+        <v>0.4399378179762578</v>
       </c>
       <c r="AO2">
-        <v>88.87356321839081</v>
+        <v>60.12727272727273</v>
       </c>
       <c r="AP2">
-        <v>-0.667902708817799</v>
+        <v>-1.644573205200679</v>
       </c>
       <c r="AQ2">
-        <v>88.87356321839081</v>
+        <v>60.12727272727273</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0848</v>
+        <v>0.0433</v>
       </c>
       <c r="E3">
-        <v>0.257</v>
+        <v>0.061</v>
       </c>
       <c r="G3">
-        <v>0.1863354037267081</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="H3">
-        <v>0.1863354037267081</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="I3">
-        <v>0.4813664596273292</v>
+        <v>0.306530612244898</v>
       </c>
       <c r="J3">
-        <v>0.4533909413567798</v>
+        <v>0.2852313913676435</v>
       </c>
       <c r="K3">
-        <v>14.5</v>
+        <v>7.01</v>
       </c>
       <c r="L3">
-        <v>0.4503105590062111</v>
+        <v>0.2861224489795918</v>
       </c>
       <c r="M3">
-        <v>6.93</v>
+        <v>4.89</v>
       </c>
       <c r="N3">
-        <v>0.0924</v>
+        <v>0.07431610942249239</v>
       </c>
       <c r="O3">
-        <v>0.4779310344827586</v>
+        <v>0.6975748930099858</v>
       </c>
       <c r="P3">
-        <v>6.93</v>
+        <v>4.89</v>
       </c>
       <c r="Q3">
-        <v>0.0924</v>
+        <v>0.07431610942249239</v>
       </c>
       <c r="R3">
-        <v>0.4779310344827586</v>
+        <v>0.6975748930099858</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="V3">
-        <v>0.156</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="W3">
-        <v>0.3519417475728155</v>
+        <v>0.137992125984252</v>
       </c>
       <c r="X3">
-        <v>0.06157748656469657</v>
+        <v>0.1014392110171034</v>
       </c>
       <c r="Y3">
-        <v>0.2903642610081189</v>
+        <v>0.03655291496714856</v>
       </c>
       <c r="Z3">
-        <v>0.9402283411685696</v>
+        <v>0.6263101385551409</v>
       </c>
       <c r="AA3">
-        <v>0.4262910126927413</v>
+        <v>0.1786433122477444</v>
       </c>
       <c r="AB3">
-        <v>0.06156757130185303</v>
+        <v>0.1014376951461799</v>
       </c>
       <c r="AC3">
-        <v>0.3647234413908883</v>
+        <v>0.07720561710156452</v>
       </c>
       <c r="AD3">
-        <v>0.033</v>
+        <v>0.003</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.033</v>
+        <v>0.003</v>
       </c>
       <c r="AG3">
-        <v>-11.667</v>
+        <v>-11.897</v>
       </c>
       <c r="AH3">
-        <v>0.0004398064851465355</v>
+        <v>4.559062656717779e-05</v>
       </c>
       <c r="AI3">
-        <v>0.0006428613172812811</v>
+        <v>6.315390606909037e-05</v>
       </c>
       <c r="AJ3">
-        <v>-0.1842167590355739</v>
+        <v>-0.2207112776654361</v>
       </c>
       <c r="AK3">
-        <v>-0.294375898872152</v>
+        <v>-0.33415723394096</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.002101910828025478</v>
+        <v>0.0003886010362694301</v>
       </c>
       <c r="AP3">
-        <v>-0.7431210191082803</v>
+        <v>-1.541062176165803</v>
       </c>
     </row>
     <row r="4">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08349999999999999</v>
+        <v>0.0645</v>
       </c>
       <c r="G4">
-        <v>0.011</v>
+        <v>-0.01478260869565217</v>
       </c>
       <c r="H4">
-        <v>0.011</v>
+        <v>-0.01478260869565217</v>
       </c>
       <c r="I4">
-        <v>-0.001894736842105263</v>
+        <v>-0.05565217391304347</v>
       </c>
       <c r="J4">
-        <v>-0.00114865066348591</v>
+        <v>-0.05565217391304347</v>
       </c>
       <c r="K4">
-        <v>0.215</v>
+        <v>-0.831</v>
       </c>
       <c r="L4">
-        <v>0.01131578947368421</v>
+        <v>-0.05161490683229813</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,7 +877,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,79 +886,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.82</v>
+        <v>2.85</v>
       </c>
       <c r="V4">
-        <v>0.9597989949748743</v>
+        <v>0.4656862745098039</v>
       </c>
       <c r="W4">
-        <v>0.02660891089108911</v>
+        <v>-0.09305711086226204</v>
       </c>
       <c r="X4">
-        <v>0.1112001642869667</v>
+        <v>0.1292880444191478</v>
       </c>
       <c r="Y4">
-        <v>-0.08459125339587761</v>
+        <v>-0.2223451552814099</v>
       </c>
       <c r="Z4">
-        <v>2.275449101796407</v>
+        <v>1.614844533600803</v>
       </c>
       <c r="AA4">
-        <v>-0.002613696120506861</v>
+        <v>-0.08986960882647944</v>
       </c>
       <c r="AB4">
-        <v>0.07374590023965857</v>
+        <v>0.1109714074466738</v>
       </c>
       <c r="AC4">
-        <v>-0.07635959636016544</v>
+        <v>-0.2008410162731533</v>
       </c>
       <c r="AD4">
-        <v>4.86</v>
+        <v>3.11</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.86</v>
+        <v>3.11</v>
       </c>
       <c r="AG4">
-        <v>1.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="AH4">
-        <v>0.5497737556561086</v>
+        <v>0.3369447453954496</v>
       </c>
       <c r="AI4">
-        <v>0.3524292965917332</v>
+        <v>0.2354277062831188</v>
       </c>
       <c r="AJ4">
-        <v>0.2071713147410359</v>
+        <v>0.04075235109717865</v>
       </c>
       <c r="AK4">
-        <v>0.1043129388164494</v>
+        <v>0.02509652509652508</v>
       </c>
       <c r="AL4">
-        <v>0.174</v>
+        <v>0.11</v>
       </c>
       <c r="AM4">
-        <v>0.174</v>
+        <v>0.11</v>
       </c>
       <c r="AN4">
-        <v>23.03317535545024</v>
+        <v>-4.829192546583851</v>
       </c>
       <c r="AO4">
-        <v>-0.2068965517241379</v>
+        <v>-8.145454545454546</v>
       </c>
       <c r="AP4">
-        <v>4.928909952606637</v>
+        <v>-0.4037267080745338</v>
       </c>
       <c r="AQ4">
-        <v>-0.2068965517241379</v>
+        <v>-8.145454545454546</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cyprus/cyprus_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0539</v>
+        <v>0.06375</v>
       </c>
       <c r="E2">
-        <v>0.061</v>
+        <v>0.181</v>
       </c>
       <c r="G2">
-        <v>0.3512807881773399</v>
+        <v>0.1401511879049676</v>
       </c>
       <c r="H2">
-        <v>0.3512807881773399</v>
+        <v>0.1401511879049676</v>
       </c>
       <c r="I2">
-        <v>0.1629064039408867</v>
+        <v>0.2300215982721383</v>
       </c>
       <c r="J2">
-        <v>0.1572466438039708</v>
+        <v>0.2225829965860796</v>
       </c>
       <c r="K2">
-        <v>6.179</v>
+        <v>10.01</v>
       </c>
       <c r="L2">
-        <v>0.152192118226601</v>
+        <v>0.2161987041036717</v>
       </c>
       <c r="M2">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="N2">
-        <v>0.06799221357063404</v>
+        <v>0.06389376096216487</v>
       </c>
       <c r="O2">
-        <v>0.7913901925877973</v>
+        <v>0.5094905094905094</v>
       </c>
       <c r="P2">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="Q2">
-        <v>0.06799221357063404</v>
+        <v>0.06389376096216487</v>
       </c>
       <c r="R2">
-        <v>0.7913901925877973</v>
+        <v>0.5094905094905094</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.75</v>
+        <v>6.16</v>
       </c>
       <c r="V2">
-        <v>0.2050889877641824</v>
+        <v>0.07717364069155601</v>
       </c>
       <c r="W2">
-        <v>0.02246750756099497</v>
+        <v>0.04857804929429113</v>
       </c>
       <c r="X2">
-        <v>0.1153636277181256</v>
+        <v>0.09341140920867644</v>
       </c>
       <c r="Y2">
-        <v>-0.09289612015713064</v>
+        <v>-0.04483335991438531</v>
       </c>
       <c r="Z2">
-        <v>0.8270860495436768</v>
+        <v>1.020408163265306</v>
       </c>
       <c r="AA2">
-        <v>0.04438685171063248</v>
+        <v>0.08465062100704616</v>
       </c>
       <c r="AB2">
-        <v>0.1062045512964268</v>
+        <v>0.08748897777308666</v>
       </c>
       <c r="AC2">
-        <v>-0.06181769958579437</v>
+        <v>-0.002838356766040495</v>
       </c>
       <c r="AD2">
-        <v>3.113</v>
+        <v>2.519</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.113</v>
+        <v>2.519</v>
       </c>
       <c r="AG2">
-        <v>-11.637</v>
+        <v>-3.641</v>
       </c>
       <c r="AH2">
-        <v>0.04148841176548985</v>
+        <v>0.03059303610682666</v>
       </c>
       <c r="AI2">
-        <v>0.05127402697939486</v>
+        <v>0.03556955054434544</v>
       </c>
       <c r="AJ2">
-        <v>-0.1930394970389662</v>
+        <v>-0.04779532417070322</v>
       </c>
       <c r="AK2">
-        <v>-0.253181907186215</v>
+        <v>-0.05631079973398909</v>
       </c>
       <c r="AL2">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AM2">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AN2">
-        <v>0.4399378179762578</v>
+        <v>0.2267326732673268</v>
       </c>
       <c r="AO2">
-        <v>60.12727272727273</v>
+        <v>88.75</v>
       </c>
       <c r="AP2">
-        <v>-1.644573205200679</v>
+        <v>-0.3277227722772277</v>
       </c>
       <c r="AQ2">
-        <v>60.12727272727273</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0433</v>
+        <v>0.068</v>
       </c>
       <c r="E3">
-        <v>0.061</v>
+        <v>0.181</v>
       </c>
       <c r="G3">
-        <v>0.5918367346938775</v>
+        <v>0.2273037542662116</v>
       </c>
       <c r="H3">
-        <v>0.5918367346938775</v>
+        <v>0.2273037542662116</v>
       </c>
       <c r="I3">
-        <v>0.306530612244898</v>
+        <v>0.4197952218430034</v>
       </c>
       <c r="J3">
-        <v>0.2852313913676435</v>
+        <v>0.392643950236706</v>
       </c>
       <c r="K3">
-        <v>7.01</v>
+        <v>11.5</v>
       </c>
       <c r="L3">
-        <v>0.2861224489795918</v>
+        <v>0.3924914675767918</v>
       </c>
       <c r="M3">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="N3">
-        <v>0.07431610942249239</v>
+        <v>0.06891891891891891</v>
       </c>
       <c r="O3">
-        <v>0.6975748930099858</v>
+        <v>0.4434782608695652</v>
       </c>
       <c r="P3">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="Q3">
-        <v>0.07431610942249239</v>
+        <v>0.06891891891891891</v>
       </c>
       <c r="R3">
-        <v>0.6975748930099858</v>
+        <v>0.4434782608695652</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.9</v>
+        <v>4.87</v>
       </c>
       <c r="V3">
-        <v>0.1808510638297872</v>
+        <v>0.06581081081081082</v>
       </c>
       <c r="W3">
-        <v>0.137992125984252</v>
+        <v>0.2446808510638298</v>
       </c>
       <c r="X3">
-        <v>0.1014392110171034</v>
+        <v>0.08477790620490791</v>
       </c>
       <c r="Y3">
-        <v>0.03655291496714856</v>
+        <v>0.1599029448589219</v>
       </c>
       <c r="Z3">
-        <v>0.6263101385551409</v>
+        <v>0.8368081338893014</v>
       </c>
       <c r="AA3">
-        <v>0.1786433122477444</v>
+        <v>0.3285676512805016</v>
       </c>
       <c r="AB3">
-        <v>0.1014376951461799</v>
+        <v>0.08477092037657963</v>
       </c>
       <c r="AC3">
-        <v>0.07720561710156452</v>
+        <v>0.243796730903922</v>
       </c>
       <c r="AD3">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="AG3">
-        <v>-11.897</v>
+        <v>-4.851</v>
       </c>
       <c r="AH3">
-        <v>4.559062656717779e-05</v>
+        <v>0.0002566908496467123</v>
       </c>
       <c r="AI3">
-        <v>6.315390606909037e-05</v>
+        <v>0.0003338076916319683</v>
       </c>
       <c r="AJ3">
-        <v>-0.2207112776654361</v>
+        <v>-0.07015285832043847</v>
       </c>
       <c r="AK3">
-        <v>-0.33415723394096</v>
+        <v>-0.09320063786047762</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.0003886010362694301</v>
+        <v>0.00152</v>
       </c>
       <c r="AP3">
-        <v>-1.541062176165803</v>
+        <v>-0.38808</v>
       </c>
     </row>
     <row r="4">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0645</v>
+        <v>0.0595</v>
       </c>
       <c r="G4">
-        <v>-0.01478260869565217</v>
+        <v>-0.01005882352941177</v>
       </c>
       <c r="H4">
-        <v>-0.01478260869565217</v>
+        <v>-0.01005882352941177</v>
       </c>
       <c r="I4">
-        <v>-0.05565217391304347</v>
+        <v>-0.09705882352941175</v>
       </c>
       <c r="J4">
-        <v>-0.05565217391304347</v>
+        <v>-0.09705882352941175</v>
       </c>
       <c r="K4">
-        <v>-0.831</v>
+        <v>-1.49</v>
       </c>
       <c r="L4">
-        <v>-0.05161490683229813</v>
+        <v>-0.08764705882352941</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.85</v>
+        <v>1.29</v>
       </c>
       <c r="V4">
-        <v>0.4656862745098039</v>
+        <v>0.2216494845360825</v>
       </c>
       <c r="W4">
-        <v>-0.09305711086226204</v>
+        <v>-0.1475247524752475</v>
       </c>
       <c r="X4">
-        <v>0.1292880444191478</v>
+        <v>0.102044912212445</v>
       </c>
       <c r="Y4">
-        <v>-0.2223451552814099</v>
+        <v>-0.2495696646876925</v>
       </c>
       <c r="Z4">
-        <v>1.614844533600803</v>
+        <v>1.640926640926641</v>
       </c>
       <c r="AA4">
-        <v>-0.08986960882647944</v>
+        <v>-0.1592664092664093</v>
       </c>
       <c r="AB4">
-        <v>0.1109714074466738</v>
+        <v>0.09020703516959369</v>
       </c>
       <c r="AC4">
-        <v>-0.2008410162731533</v>
+        <v>-0.2494734444360029</v>
       </c>
       <c r="AD4">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="AG4">
-        <v>0.2599999999999998</v>
+        <v>1.21</v>
       </c>
       <c r="AH4">
-        <v>0.3369447453954496</v>
+        <v>0.3004807692307692</v>
       </c>
       <c r="AI4">
-        <v>0.2354277062831188</v>
+        <v>0.1798561151079137</v>
       </c>
       <c r="AJ4">
-        <v>0.04075235109717865</v>
+        <v>0.1721194879089616</v>
       </c>
       <c r="AK4">
-        <v>0.02509652509652508</v>
+        <v>0.09595559080095163</v>
       </c>
       <c r="AL4">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AM4">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AN4">
-        <v>-4.829192546583851</v>
+        <v>-1.798561151079137</v>
       </c>
       <c r="AO4">
-        <v>-8.145454545454546</v>
+        <v>-13.75</v>
       </c>
       <c r="AP4">
-        <v>-0.4037267080745338</v>
+        <v>-0.8705035971223022</v>
       </c>
       <c r="AQ4">
-        <v>-8.145454545454546</v>
+        <v>-13.75</v>
       </c>
     </row>
   </sheetData>
